--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.28125</v>
+        <v>0.4060150375939849</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3142857142857143</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="D2">
-        <v>0.7272727272727273</v>
+        <v>0.6029411764705882</v>
       </c>
       <c r="E2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
